--- a/Informes (GANTT, INFORME PDF, CRONOGRAMAS, MANUALES)/Diagrama de Gantt - UGV Autonomo.xlsx
+++ b/Informes (GANTT, INFORME PDF, CRONOGRAMAS, MANUALES)/Diagrama de Gantt - UGV Autonomo.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9108"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7980"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
   <si>
     <t>TAREA</t>
   </si>
@@ -39,9 +39,6 @@
   </si>
   <si>
     <t>FIN</t>
-  </si>
-  <si>
-    <t>Persona X</t>
   </si>
   <si>
     <t>INICIO DEL PROYECTO</t>
@@ -98,13 +95,7 @@
     <t>4.4 Ensamble mecánico del robot</t>
   </si>
   <si>
-    <t>4.5 Integración electrónica y programacion</t>
-  </si>
-  <si>
     <t>4.6 Ajustes</t>
-  </si>
-  <si>
-    <t>FASE 5 - INTEGRACION DE SOFTWARE Y PRUEBAS REALES</t>
   </si>
   <si>
     <t>5.2 Calibracion y prueba final</t>
@@ -156,6 +147,36 @@
   </si>
   <si>
     <t>Horas Totales</t>
+  </si>
+  <si>
+    <t>Gutierrez/Venieri</t>
+  </si>
+  <si>
+    <t>Venieri</t>
+  </si>
+  <si>
+    <t>Servando</t>
+  </si>
+  <si>
+    <t>Venieri/Gutierrez</t>
+  </si>
+  <si>
+    <t>FASE 5 - INTEGRACION DE SOFTWARE Y PRUEBAS</t>
+  </si>
+  <si>
+    <t>PREDECESORA</t>
+  </si>
+  <si>
+    <t>2.1</t>
+  </si>
+  <si>
+    <t>4.5 electrónica y programacion</t>
+  </si>
+  <si>
+    <t>Venieri/Servando</t>
+  </si>
+  <si>
+    <t>2.1/3.1</t>
   </si>
 </sst>
 </file>
@@ -604,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -727,6 +748,18 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -735,6 +768,9 @@
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -746,12 +782,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -818,7 +848,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="22" fmlaLink="$F$5" horiz="1" max="98" page="10" val="45"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Scroll" dx="22" fmlaLink="$G$5" horiz="1" max="98" page="10" val="25"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -827,16 +857,16 @@
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
-          <xdr:col>2</xdr:col>
+          <xdr:col>3</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>15240</xdr:rowOff>
+          <xdr:row>3</xdr:row>
+          <xdr:rowOff>209550</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>8</xdr:col>
-          <xdr:colOff>297180</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>220980</xdr:rowOff>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>5</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -1174,1082 +1204,1087 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:DI44"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B3:DJ44"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.44140625" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" customWidth="1"/>
-    <col min="4" max="4" width="10.21875" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="1"/>
-    <col min="8" max="8" width="1.109375" customWidth="1"/>
-    <col min="9" max="140" width="4.6640625" customWidth="1"/>
+    <col min="1" max="1" width="1.42578125" customWidth="1"/>
+    <col min="2" max="2" width="42.28515625" customWidth="1"/>
+    <col min="3" max="3" width="16" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" style="1"/>
+    <col min="9" max="9" width="1.140625" customWidth="1"/>
+    <col min="10" max="141" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:113" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:114" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B3" s="59"/>
       <c r="C3" s="59"/>
       <c r="D3" s="59"/>
       <c r="E3" s="59"/>
       <c r="F3" s="59"/>
       <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
     </row>
-    <row r="4" spans="2:113" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="I4" s="6"/>
+    <row r="4" spans="2:114" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="2:113" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F5" s="27">
-        <v>45</v>
-      </c>
-      <c r="G5" s="28">
-        <f>F6+F5</f>
-        <v>46289</v>
-      </c>
-      <c r="I5" s="52">
-        <f>I6</f>
-        <v>46289</v>
-      </c>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-      <c r="M5" s="53"/>
-      <c r="N5" s="53"/>
-      <c r="O5" s="54"/>
-      <c r="P5" s="52">
-        <f>P6</f>
-        <v>46296</v>
-      </c>
-      <c r="Q5" s="53"/>
-      <c r="R5" s="53"/>
-      <c r="S5" s="53"/>
-      <c r="T5" s="53"/>
-      <c r="U5" s="53"/>
-      <c r="V5" s="54"/>
-      <c r="W5" s="52">
-        <f t="shared" ref="W5" si="0">W6</f>
-        <v>46303</v>
-      </c>
-      <c r="X5" s="53"/>
-      <c r="Y5" s="53"/>
-      <c r="Z5" s="53"/>
-      <c r="AA5" s="53"/>
-      <c r="AB5" s="53"/>
-      <c r="AC5" s="54"/>
-      <c r="AD5" s="52">
-        <f t="shared" ref="AD5" si="1">AD6</f>
-        <v>46310</v>
-      </c>
-      <c r="AE5" s="53"/>
-      <c r="AF5" s="53"/>
-      <c r="AG5" s="53"/>
-      <c r="AH5" s="53"/>
-      <c r="AI5" s="53"/>
-      <c r="AJ5" s="54"/>
-      <c r="AK5" s="52">
-        <f t="shared" ref="AK5" si="2">AK6</f>
-        <v>46317</v>
-      </c>
-      <c r="AL5" s="53"/>
-      <c r="AM5" s="53"/>
-      <c r="AN5" s="53"/>
-      <c r="AO5" s="53"/>
-      <c r="AP5" s="53"/>
-      <c r="AQ5" s="54"/>
-      <c r="AR5" s="52">
-        <f t="shared" ref="AR5" si="3">AR6</f>
-        <v>46324</v>
-      </c>
-      <c r="AS5" s="53"/>
-      <c r="AT5" s="53"/>
-      <c r="AU5" s="53"/>
-      <c r="AV5" s="53"/>
-      <c r="AW5" s="53"/>
-      <c r="AX5" s="54"/>
-      <c r="AY5" s="52">
-        <f t="shared" ref="AY5" si="4">AY6</f>
-        <v>46331</v>
-      </c>
-      <c r="AZ5" s="53"/>
-      <c r="BA5" s="53"/>
-      <c r="BB5" s="53"/>
-      <c r="BC5" s="53"/>
-      <c r="BD5" s="53"/>
-      <c r="BE5" s="54"/>
-      <c r="BF5" s="52">
-        <f t="shared" ref="BF5" si="5">BF6</f>
-        <v>46338</v>
-      </c>
-      <c r="BG5" s="53"/>
-      <c r="BH5" s="53"/>
-      <c r="BI5" s="53"/>
-      <c r="BJ5" s="53"/>
-      <c r="BK5" s="53"/>
-      <c r="BL5" s="54"/>
-      <c r="BM5" s="52">
-        <f t="shared" ref="BM5" si="6">BM6</f>
-        <v>46345</v>
-      </c>
-      <c r="BN5" s="53"/>
-      <c r="BO5" s="53"/>
-      <c r="BP5" s="53"/>
-      <c r="BQ5" s="53"/>
-      <c r="BR5" s="53"/>
-      <c r="BS5" s="54"/>
-      <c r="BT5" s="52">
-        <f t="shared" ref="BT5" si="7">BT6</f>
-        <v>46352</v>
-      </c>
-      <c r="BU5" s="53"/>
-      <c r="BV5" s="53"/>
-      <c r="BW5" s="53"/>
-      <c r="BX5" s="53"/>
-      <c r="BY5" s="53"/>
-      <c r="BZ5" s="54"/>
-      <c r="CA5" s="52">
-        <f t="shared" ref="CA5" si="8">CA6</f>
-        <v>46359</v>
-      </c>
-      <c r="CB5" s="53"/>
-      <c r="CC5" s="53"/>
-      <c r="CD5" s="53"/>
-      <c r="CE5" s="53"/>
-      <c r="CF5" s="53"/>
-      <c r="CG5" s="54"/>
-      <c r="CH5" s="52">
-        <f t="shared" ref="CH5" si="9">CH6</f>
-        <v>46366</v>
-      </c>
-      <c r="CI5" s="53"/>
-      <c r="CJ5" s="53"/>
-      <c r="CK5" s="53"/>
-      <c r="CL5" s="53"/>
-      <c r="CM5" s="53"/>
-      <c r="CN5" s="54"/>
-      <c r="CO5" s="52">
-        <f t="shared" ref="CO5" si="10">CO6</f>
-        <v>46373</v>
-      </c>
-      <c r="CP5" s="53"/>
-      <c r="CQ5" s="53"/>
-      <c r="CR5" s="53"/>
-      <c r="CS5" s="53"/>
-      <c r="CT5" s="53"/>
-      <c r="CU5" s="54"/>
-      <c r="CV5" s="52">
-        <f t="shared" ref="CV5" si="11">CV6</f>
-        <v>46380</v>
-      </c>
-      <c r="CW5" s="53"/>
-      <c r="CX5" s="53"/>
-      <c r="CY5" s="53"/>
-      <c r="CZ5" s="53"/>
-      <c r="DA5" s="53"/>
-      <c r="DB5" s="54"/>
-      <c r="DC5" s="52">
-        <f t="shared" ref="DC5" si="12">DC6</f>
-        <v>46387</v>
-      </c>
-      <c r="DD5" s="53"/>
-      <c r="DE5" s="53"/>
-      <c r="DF5" s="53"/>
-      <c r="DG5" s="53"/>
-      <c r="DH5" s="53"/>
-      <c r="DI5" s="54"/>
+    <row r="5" spans="2:114" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G5" s="27">
+        <v>25</v>
+      </c>
+      <c r="H5" s="28">
+        <f>G6+G5</f>
+        <v>46269</v>
+      </c>
+      <c r="J5" s="56">
+        <f>J6</f>
+        <v>46269</v>
+      </c>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="56">
+        <f>Q6</f>
+        <v>46276</v>
+      </c>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="58"/>
+      <c r="X5" s="56">
+        <f>X6</f>
+        <v>46283</v>
+      </c>
+      <c r="Y5" s="57"/>
+      <c r="Z5" s="57"/>
+      <c r="AA5" s="57"/>
+      <c r="AB5" s="57"/>
+      <c r="AC5" s="57"/>
+      <c r="AD5" s="58"/>
+      <c r="AE5" s="56">
+        <f>AE6</f>
+        <v>46290</v>
+      </c>
+      <c r="AF5" s="57"/>
+      <c r="AG5" s="57"/>
+      <c r="AH5" s="57"/>
+      <c r="AI5" s="57"/>
+      <c r="AJ5" s="57"/>
+      <c r="AK5" s="58"/>
+      <c r="AL5" s="56">
+        <f>AL6</f>
+        <v>46297</v>
+      </c>
+      <c r="AM5" s="57"/>
+      <c r="AN5" s="57"/>
+      <c r="AO5" s="57"/>
+      <c r="AP5" s="57"/>
+      <c r="AQ5" s="57"/>
+      <c r="AR5" s="58"/>
+      <c r="AS5" s="56">
+        <f>AS6</f>
+        <v>46304</v>
+      </c>
+      <c r="AT5" s="57"/>
+      <c r="AU5" s="57"/>
+      <c r="AV5" s="57"/>
+      <c r="AW5" s="57"/>
+      <c r="AX5" s="57"/>
+      <c r="AY5" s="58"/>
+      <c r="AZ5" s="56">
+        <f>AZ6</f>
+        <v>46311</v>
+      </c>
+      <c r="BA5" s="57"/>
+      <c r="BB5" s="57"/>
+      <c r="BC5" s="57"/>
+      <c r="BD5" s="57"/>
+      <c r="BE5" s="57"/>
+      <c r="BF5" s="58"/>
+      <c r="BG5" s="56">
+        <f>BG6</f>
+        <v>46318</v>
+      </c>
+      <c r="BH5" s="57"/>
+      <c r="BI5" s="57"/>
+      <c r="BJ5" s="57"/>
+      <c r="BK5" s="57"/>
+      <c r="BL5" s="57"/>
+      <c r="BM5" s="58"/>
+      <c r="BN5" s="56">
+        <f>BN6</f>
+        <v>46325</v>
+      </c>
+      <c r="BO5" s="57"/>
+      <c r="BP5" s="57"/>
+      <c r="BQ5" s="57"/>
+      <c r="BR5" s="57"/>
+      <c r="BS5" s="57"/>
+      <c r="BT5" s="58"/>
+      <c r="BU5" s="56">
+        <f>BU6</f>
+        <v>46332</v>
+      </c>
+      <c r="BV5" s="57"/>
+      <c r="BW5" s="57"/>
+      <c r="BX5" s="57"/>
+      <c r="BY5" s="57"/>
+      <c r="BZ5" s="57"/>
+      <c r="CA5" s="58"/>
+      <c r="CB5" s="56">
+        <f>CB6</f>
+        <v>46339</v>
+      </c>
+      <c r="CC5" s="57"/>
+      <c r="CD5" s="57"/>
+      <c r="CE5" s="57"/>
+      <c r="CF5" s="57"/>
+      <c r="CG5" s="57"/>
+      <c r="CH5" s="58"/>
+      <c r="CI5" s="56">
+        <f>CI6</f>
+        <v>46346</v>
+      </c>
+      <c r="CJ5" s="57"/>
+      <c r="CK5" s="57"/>
+      <c r="CL5" s="57"/>
+      <c r="CM5" s="57"/>
+      <c r="CN5" s="57"/>
+      <c r="CO5" s="58"/>
+      <c r="CP5" s="56">
+        <f>CP6</f>
+        <v>46353</v>
+      </c>
+      <c r="CQ5" s="57"/>
+      <c r="CR5" s="57"/>
+      <c r="CS5" s="57"/>
+      <c r="CT5" s="57"/>
+      <c r="CU5" s="57"/>
+      <c r="CV5" s="58"/>
+      <c r="CW5" s="56">
+        <f>CW6</f>
+        <v>46360</v>
+      </c>
+      <c r="CX5" s="57"/>
+      <c r="CY5" s="57"/>
+      <c r="CZ5" s="57"/>
+      <c r="DA5" s="57"/>
+      <c r="DB5" s="57"/>
+      <c r="DC5" s="58"/>
+      <c r="DD5" s="56">
+        <f>DD6</f>
+        <v>46367</v>
+      </c>
+      <c r="DE5" s="57"/>
+      <c r="DF5" s="57"/>
+      <c r="DG5" s="57"/>
+      <c r="DH5" s="57"/>
+      <c r="DI5" s="57"/>
+      <c r="DJ5" s="58"/>
     </row>
-    <row r="6" spans="2:113" x14ac:dyDescent="0.3">
-      <c r="C6" s="57" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="55">
+    <row r="6" spans="2:114" x14ac:dyDescent="0.25">
+      <c r="D6" s="62" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="60">
         <v>46244</v>
       </c>
-      <c r="G6" s="56"/>
-      <c r="I6" s="3">
-        <f>G5</f>
-        <v>46289</v>
-      </c>
-      <c r="J6" s="4">
-        <f>I6+1</f>
-        <v>46290</v>
+      <c r="H6" s="61"/>
+      <c r="J6" s="3">
+        <f>H5</f>
+        <v>46269</v>
       </c>
       <c r="K6" s="4">
         <f>J6+1</f>
+        <v>46270</v>
+      </c>
+      <c r="L6" s="4">
+        <f>K6+1</f>
+        <v>46271</v>
+      </c>
+      <c r="M6" s="4">
+        <f t="shared" ref="M6:BX6" si="0">L6+1</f>
+        <v>46272</v>
+      </c>
+      <c r="N6" s="4">
+        <f t="shared" si="0"/>
+        <v>46273</v>
+      </c>
+      <c r="O6" s="4">
+        <f t="shared" si="0"/>
+        <v>46274</v>
+      </c>
+      <c r="P6" s="5">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="Q6" s="3">
+        <f t="shared" si="0"/>
+        <v>46276</v>
+      </c>
+      <c r="R6" s="4">
+        <f t="shared" si="0"/>
+        <v>46277</v>
+      </c>
+      <c r="S6" s="4">
+        <f t="shared" si="0"/>
+        <v>46278</v>
+      </c>
+      <c r="T6" s="4">
+        <f t="shared" si="0"/>
+        <v>46279</v>
+      </c>
+      <c r="U6" s="4">
+        <f t="shared" si="0"/>
+        <v>46280</v>
+      </c>
+      <c r="V6" s="4">
+        <f t="shared" si="0"/>
+        <v>46281</v>
+      </c>
+      <c r="W6" s="5">
+        <f t="shared" si="0"/>
+        <v>46282</v>
+      </c>
+      <c r="X6" s="3">
+        <f t="shared" si="0"/>
+        <v>46283</v>
+      </c>
+      <c r="Y6" s="4">
+        <f t="shared" si="0"/>
+        <v>46284</v>
+      </c>
+      <c r="Z6" s="4">
+        <f t="shared" si="0"/>
+        <v>46285</v>
+      </c>
+      <c r="AA6" s="4">
+        <f t="shared" si="0"/>
+        <v>46286</v>
+      </c>
+      <c r="AB6" s="4">
+        <f t="shared" si="0"/>
+        <v>46287</v>
+      </c>
+      <c r="AC6" s="4">
+        <f t="shared" si="0"/>
+        <v>46288</v>
+      </c>
+      <c r="AD6" s="5">
+        <f t="shared" si="0"/>
+        <v>46289</v>
+      </c>
+      <c r="AE6" s="3">
+        <f t="shared" si="0"/>
+        <v>46290</v>
+      </c>
+      <c r="AF6" s="15">
+        <f t="shared" si="0"/>
         <v>46291</v>
       </c>
-      <c r="L6" s="4">
-        <f t="shared" ref="L6:BW6" si="13">K6+1</f>
+      <c r="AG6" s="15">
+        <f t="shared" si="0"/>
         <v>46292</v>
       </c>
-      <c r="M6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AH6" s="15">
+        <f t="shared" si="0"/>
         <v>46293</v>
       </c>
-      <c r="N6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AI6" s="15">
+        <f t="shared" si="0"/>
         <v>46294</v>
       </c>
-      <c r="O6" s="5">
-        <f t="shared" si="13"/>
+      <c r="AJ6" s="15">
+        <f t="shared" si="0"/>
         <v>46295</v>
       </c>
-      <c r="P6" s="3">
-        <f t="shared" si="13"/>
+      <c r="AK6" s="16">
+        <f t="shared" si="0"/>
         <v>46296</v>
       </c>
-      <c r="Q6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AL6" s="17">
+        <f t="shared" si="0"/>
         <v>46297</v>
       </c>
-      <c r="R6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AM6" s="15">
+        <f t="shared" si="0"/>
         <v>46298</v>
       </c>
-      <c r="S6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AN6" s="15">
+        <f t="shared" si="0"/>
         <v>46299</v>
       </c>
-      <c r="T6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AO6" s="15">
+        <f t="shared" si="0"/>
         <v>46300</v>
       </c>
-      <c r="U6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AP6" s="15">
+        <f t="shared" si="0"/>
         <v>46301</v>
       </c>
-      <c r="V6" s="5">
-        <f t="shared" si="13"/>
+      <c r="AQ6" s="15">
+        <f t="shared" si="0"/>
         <v>46302</v>
       </c>
-      <c r="W6" s="3">
-        <f t="shared" si="13"/>
+      <c r="AR6" s="16">
+        <f t="shared" si="0"/>
         <v>46303</v>
       </c>
-      <c r="X6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AS6" s="17">
+        <f t="shared" si="0"/>
         <v>46304</v>
       </c>
-      <c r="Y6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AT6" s="15">
+        <f t="shared" si="0"/>
         <v>46305</v>
       </c>
-      <c r="Z6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AU6" s="15">
+        <f t="shared" si="0"/>
         <v>46306</v>
       </c>
-      <c r="AA6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AV6" s="15">
+        <f t="shared" si="0"/>
         <v>46307</v>
       </c>
-      <c r="AB6" s="4">
-        <f t="shared" si="13"/>
+      <c r="AW6" s="15">
+        <f t="shared" si="0"/>
         <v>46308</v>
       </c>
-      <c r="AC6" s="5">
-        <f t="shared" si="13"/>
+      <c r="AX6" s="15">
+        <f t="shared" si="0"/>
         <v>46309</v>
       </c>
-      <c r="AD6" s="3">
-        <f t="shared" si="13"/>
+      <c r="AY6" s="16">
+        <f t="shared" si="0"/>
         <v>46310</v>
       </c>
-      <c r="AE6" s="15">
-        <f t="shared" si="13"/>
+      <c r="AZ6" s="17">
+        <f t="shared" si="0"/>
         <v>46311</v>
       </c>
-      <c r="AF6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BA6" s="15">
+        <f t="shared" si="0"/>
         <v>46312</v>
       </c>
-      <c r="AG6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BB6" s="15">
+        <f t="shared" si="0"/>
         <v>46313</v>
       </c>
-      <c r="AH6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BC6" s="15">
+        <f t="shared" si="0"/>
         <v>46314</v>
       </c>
-      <c r="AI6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BD6" s="15">
+        <f t="shared" si="0"/>
         <v>46315</v>
       </c>
-      <c r="AJ6" s="16">
-        <f t="shared" si="13"/>
+      <c r="BE6" s="15">
+        <f t="shared" si="0"/>
         <v>46316</v>
       </c>
-      <c r="AK6" s="17">
-        <f t="shared" si="13"/>
+      <c r="BF6" s="16">
+        <f t="shared" si="0"/>
         <v>46317</v>
       </c>
-      <c r="AL6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BG6" s="17">
+        <f t="shared" si="0"/>
         <v>46318</v>
       </c>
-      <c r="AM6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BH6" s="15">
+        <f t="shared" si="0"/>
         <v>46319</v>
       </c>
-      <c r="AN6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BI6" s="15">
+        <f t="shared" si="0"/>
         <v>46320</v>
       </c>
-      <c r="AO6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BJ6" s="19">
+        <f t="shared" si="0"/>
         <v>46321</v>
       </c>
-      <c r="AP6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BK6" s="19">
+        <f t="shared" si="0"/>
         <v>46322</v>
       </c>
-      <c r="AQ6" s="16">
-        <f t="shared" si="13"/>
+      <c r="BL6" s="19">
+        <f t="shared" si="0"/>
         <v>46323</v>
       </c>
-      <c r="AR6" s="17">
-        <f t="shared" si="13"/>
+      <c r="BM6" s="20">
+        <f t="shared" si="0"/>
         <v>46324</v>
       </c>
-      <c r="AS6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BN6" s="18">
+        <f t="shared" si="0"/>
         <v>46325</v>
       </c>
-      <c r="AT6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BO6" s="19">
+        <f t="shared" si="0"/>
         <v>46326</v>
       </c>
-      <c r="AU6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BP6" s="19">
+        <f t="shared" si="0"/>
         <v>46327</v>
       </c>
-      <c r="AV6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BQ6" s="19">
+        <f t="shared" si="0"/>
         <v>46328</v>
       </c>
-      <c r="AW6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BR6" s="19">
+        <f t="shared" si="0"/>
         <v>46329</v>
       </c>
-      <c r="AX6" s="16">
-        <f t="shared" si="13"/>
+      <c r="BS6" s="19">
+        <f t="shared" si="0"/>
         <v>46330</v>
       </c>
-      <c r="AY6" s="17">
-        <f t="shared" si="13"/>
+      <c r="BT6" s="20">
+        <f t="shared" si="0"/>
         <v>46331</v>
       </c>
-      <c r="AZ6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BU6" s="18">
+        <f t="shared" si="0"/>
         <v>46332</v>
       </c>
-      <c r="BA6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BV6" s="19">
+        <f t="shared" si="0"/>
         <v>46333</v>
       </c>
-      <c r="BB6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BW6" s="19">
+        <f t="shared" si="0"/>
         <v>46334</v>
       </c>
-      <c r="BC6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BX6" s="19">
+        <f t="shared" si="0"/>
         <v>46335</v>
       </c>
-      <c r="BD6" s="15">
-        <f t="shared" si="13"/>
+      <c r="BY6" s="19">
+        <f t="shared" ref="BY6:CH6" si="1">BX6+1</f>
         <v>46336</v>
       </c>
-      <c r="BE6" s="16">
-        <f t="shared" si="13"/>
+      <c r="BZ6" s="19">
+        <f t="shared" si="1"/>
         <v>46337</v>
       </c>
-      <c r="BF6" s="17">
-        <f t="shared" si="13"/>
+      <c r="CA6" s="20">
+        <f t="shared" si="1"/>
         <v>46338</v>
       </c>
-      <c r="BG6" s="15">
-        <f t="shared" si="13"/>
+      <c r="CB6" s="43">
+        <f>CA6+1</f>
         <v>46339</v>
       </c>
-      <c r="BH6" s="15">
-        <f t="shared" si="13"/>
+      <c r="CC6" s="44">
+        <f t="shared" si="1"/>
         <v>46340</v>
       </c>
-      <c r="BI6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CD6" s="44">
+        <f t="shared" si="1"/>
         <v>46341</v>
       </c>
-      <c r="BJ6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CE6" s="44">
+        <f t="shared" si="1"/>
         <v>46342</v>
       </c>
-      <c r="BK6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CF6" s="44">
+        <f t="shared" si="1"/>
         <v>46343</v>
       </c>
-      <c r="BL6" s="20">
-        <f t="shared" si="13"/>
+      <c r="CG6" s="44">
+        <f t="shared" si="1"/>
         <v>46344</v>
       </c>
-      <c r="BM6" s="18">
-        <f t="shared" si="13"/>
+      <c r="CH6" s="44">
+        <f t="shared" si="1"/>
         <v>46345</v>
       </c>
-      <c r="BN6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CI6" s="44">
+        <f t="shared" ref="CI6:DJ6" si="2">CH6+1</f>
         <v>46346</v>
       </c>
-      <c r="BO6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CJ6" s="44">
+        <f t="shared" si="2"/>
         <v>46347</v>
       </c>
-      <c r="BP6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CK6" s="44">
+        <f t="shared" si="2"/>
         <v>46348</v>
       </c>
-      <c r="BQ6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CL6" s="44">
+        <f t="shared" si="2"/>
         <v>46349</v>
       </c>
-      <c r="BR6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CM6" s="44">
+        <f t="shared" si="2"/>
         <v>46350</v>
       </c>
-      <c r="BS6" s="20">
-        <f t="shared" si="13"/>
+      <c r="CN6" s="44">
+        <f t="shared" si="2"/>
         <v>46351</v>
       </c>
-      <c r="BT6" s="18">
-        <f t="shared" si="13"/>
+      <c r="CO6" s="44">
+        <f t="shared" si="2"/>
         <v>46352</v>
       </c>
-      <c r="BU6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CP6" s="44">
+        <f t="shared" si="2"/>
         <v>46353</v>
       </c>
-      <c r="BV6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CQ6" s="44">
+        <f t="shared" si="2"/>
         <v>46354</v>
       </c>
-      <c r="BW6" s="19">
-        <f t="shared" si="13"/>
+      <c r="CR6" s="44">
+        <f t="shared" si="2"/>
         <v>46355</v>
       </c>
-      <c r="BX6" s="19">
-        <f t="shared" ref="BX6:CG6" si="14">BW6+1</f>
+      <c r="CS6" s="44">
+        <f t="shared" si="2"/>
         <v>46356</v>
       </c>
-      <c r="BY6" s="19">
-        <f t="shared" si="14"/>
+      <c r="CT6" s="44">
+        <f t="shared" si="2"/>
         <v>46357</v>
       </c>
-      <c r="BZ6" s="20">
-        <f t="shared" si="14"/>
+      <c r="CU6" s="44">
+        <f t="shared" si="2"/>
         <v>46358</v>
       </c>
-      <c r="CA6" s="43">
-        <f>BZ6+1</f>
+      <c r="CV6" s="44">
+        <f t="shared" si="2"/>
         <v>46359</v>
       </c>
-      <c r="CB6" s="44">
-        <f t="shared" si="14"/>
+      <c r="CW6" s="44">
+        <f t="shared" si="2"/>
         <v>46360</v>
       </c>
-      <c r="CC6" s="44">
-        <f t="shared" si="14"/>
+      <c r="CX6" s="44">
+        <f t="shared" si="2"/>
         <v>46361</v>
       </c>
-      <c r="CD6" s="44">
-        <f t="shared" si="14"/>
+      <c r="CY6" s="44">
+        <f t="shared" si="2"/>
         <v>46362</v>
       </c>
-      <c r="CE6" s="44">
-        <f t="shared" si="14"/>
+      <c r="CZ6" s="44">
+        <f t="shared" si="2"/>
         <v>46363</v>
       </c>
-      <c r="CF6" s="44">
-        <f t="shared" si="14"/>
+      <c r="DA6" s="44">
+        <f t="shared" si="2"/>
         <v>46364</v>
       </c>
-      <c r="CG6" s="44">
-        <f t="shared" si="14"/>
+      <c r="DB6" s="44">
+        <f t="shared" si="2"/>
         <v>46365</v>
       </c>
-      <c r="CH6" s="44">
-        <f t="shared" ref="CH6" si="15">CG6+1</f>
+      <c r="DC6" s="44">
+        <f t="shared" si="2"/>
         <v>46366</v>
       </c>
-      <c r="CI6" s="44">
-        <f t="shared" ref="CI6" si="16">CH6+1</f>
+      <c r="DD6" s="44">
+        <f t="shared" si="2"/>
         <v>46367</v>
       </c>
-      <c r="CJ6" s="44">
-        <f t="shared" ref="CJ6" si="17">CI6+1</f>
+      <c r="DE6" s="44">
+        <f t="shared" si="2"/>
         <v>46368</v>
       </c>
-      <c r="CK6" s="44">
-        <f t="shared" ref="CK6" si="18">CJ6+1</f>
+      <c r="DF6" s="44">
+        <f t="shared" si="2"/>
         <v>46369</v>
       </c>
-      <c r="CL6" s="44">
-        <f t="shared" ref="CL6" si="19">CK6+1</f>
+      <c r="DG6" s="44">
+        <f t="shared" si="2"/>
         <v>46370</v>
       </c>
-      <c r="CM6" s="44">
-        <f t="shared" ref="CM6" si="20">CL6+1</f>
+      <c r="DH6" s="44">
+        <f t="shared" si="2"/>
         <v>46371</v>
       </c>
-      <c r="CN6" s="44">
-        <f t="shared" ref="CN6" si="21">CM6+1</f>
+      <c r="DI6" s="44">
+        <f t="shared" si="2"/>
         <v>46372</v>
       </c>
-      <c r="CO6" s="44">
-        <f t="shared" ref="CO6" si="22">CN6+1</f>
+      <c r="DJ6" s="50">
+        <f t="shared" si="2"/>
         <v>46373</v>
       </c>
-      <c r="CP6" s="44">
-        <f t="shared" ref="CP6" si="23">CO6+1</f>
-        <v>46374</v>
-      </c>
-      <c r="CQ6" s="44">
-        <f t="shared" ref="CQ6" si="24">CP6+1</f>
-        <v>46375</v>
-      </c>
-      <c r="CR6" s="44">
-        <f t="shared" ref="CR6" si="25">CQ6+1</f>
-        <v>46376</v>
-      </c>
-      <c r="CS6" s="44">
-        <f t="shared" ref="CS6" si="26">CR6+1</f>
-        <v>46377</v>
-      </c>
-      <c r="CT6" s="44">
-        <f t="shared" ref="CT6" si="27">CS6+1</f>
-        <v>46378</v>
-      </c>
-      <c r="CU6" s="44">
-        <f t="shared" ref="CU6" si="28">CT6+1</f>
-        <v>46379</v>
-      </c>
-      <c r="CV6" s="44">
-        <f t="shared" ref="CV6" si="29">CU6+1</f>
-        <v>46380</v>
-      </c>
-      <c r="CW6" s="44">
-        <f t="shared" ref="CW6" si="30">CV6+1</f>
-        <v>46381</v>
-      </c>
-      <c r="CX6" s="44">
-        <f t="shared" ref="CX6" si="31">CW6+1</f>
-        <v>46382</v>
-      </c>
-      <c r="CY6" s="44">
-        <f t="shared" ref="CY6" si="32">CX6+1</f>
-        <v>46383</v>
-      </c>
-      <c r="CZ6" s="44">
-        <f t="shared" ref="CZ6" si="33">CY6+1</f>
-        <v>46384</v>
-      </c>
-      <c r="DA6" s="44">
-        <f t="shared" ref="DA6" si="34">CZ6+1</f>
-        <v>46385</v>
-      </c>
-      <c r="DB6" s="44">
-        <f t="shared" ref="DB6" si="35">DA6+1</f>
-        <v>46386</v>
-      </c>
-      <c r="DC6" s="44">
-        <f t="shared" ref="DC6" si="36">DB6+1</f>
-        <v>46387</v>
-      </c>
-      <c r="DD6" s="44">
-        <f t="shared" ref="DD6" si="37">DC6+1</f>
-        <v>46388</v>
-      </c>
-      <c r="DE6" s="44">
-        <f t="shared" ref="DE6" si="38">DD6+1</f>
-        <v>46389</v>
-      </c>
-      <c r="DF6" s="44">
-        <f t="shared" ref="DF6" si="39">DE6+1</f>
-        <v>46390</v>
-      </c>
-      <c r="DG6" s="44">
-        <f t="shared" ref="DG6" si="40">DF6+1</f>
-        <v>46391</v>
-      </c>
-      <c r="DH6" s="44">
-        <f t="shared" ref="DH6" si="41">DG6+1</f>
-        <v>46392</v>
-      </c>
-      <c r="DI6" s="50">
-        <f t="shared" ref="DI6" si="42">DH6+1</f>
-        <v>46393</v>
-      </c>
     </row>
-    <row r="7" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="H7" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="37"/>
-      <c r="I7" s="22" t="str">
-        <f>(UPPER(LEFT(TEXT(I6,"DDD"),1)))</f>
+      <c r="I7" s="37"/>
+      <c r="J7" s="22" t="str">
+        <f>(UPPER(LEFT(TEXT(J6,"DDD"),1)))</f>
+        <v>V</v>
+      </c>
+      <c r="K7" s="22" t="str">
+        <f t="shared" ref="K7:BV7" si="3">(UPPER(LEFT(TEXT(K6,"DDD"))))</f>
+        <v>S</v>
+      </c>
+      <c r="L7" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>D</v>
+      </c>
+      <c r="M7" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>L</v>
+      </c>
+      <c r="N7" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>M</v>
+      </c>
+      <c r="O7" s="22" t="str">
+        <f t="shared" si="3"/>
+        <v>M</v>
+      </c>
+      <c r="P7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="J7" s="22" t="str">
-        <f t="shared" ref="J7:BU7" si="43">(UPPER(LEFT(TEXT(J6,"DDD"))))</f>
+      <c r="Q7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="K7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="R7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="L7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="S7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="M7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="T7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="N7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="U7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="O7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="V7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="P7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="W7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="Q7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="X7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="R7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="Y7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="S7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="Z7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="T7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AA7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="U7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AB7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="V7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AC7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="W7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AD7" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="X7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AE7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="Y7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AF7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="Z7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AG7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="AA7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AH7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="AB7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AI7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AC7" s="23" t="str">
-        <f t="shared" si="43"/>
+      <c r="AJ7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AD7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AK7" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="AE7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AL7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="AF7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AM7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="AG7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AN7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="AH7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AO7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="AI7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AP7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AJ7" s="23" t="str">
-        <f t="shared" si="43"/>
+      <c r="AQ7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AK7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AR7" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="AL7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AS7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="AM7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AT7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="AN7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AU7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="AO7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AV7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="AP7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AW7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AQ7" s="23" t="str">
-        <f t="shared" si="43"/>
+      <c r="AX7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AR7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AY7" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="AS7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="AZ7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="AT7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BA7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="AU7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BB7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="AV7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BC7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="AW7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BD7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AX7" s="23" t="str">
-        <f t="shared" si="43"/>
+      <c r="BE7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="AY7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BF7" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="AZ7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BG7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="BA7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BH7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="BB7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BI7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="BC7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BJ7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="BD7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BK7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="BE7" s="23" t="str">
-        <f t="shared" si="43"/>
+      <c r="BL7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="BF7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BM7" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="BG7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BN7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="BH7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BO7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="BI7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BP7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>D</v>
       </c>
-      <c r="BJ7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BQ7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>L</v>
       </c>
-      <c r="BK7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BR7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="BL7" s="23" t="str">
-        <f t="shared" si="43"/>
+      <c r="BS7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>M</v>
       </c>
-      <c r="BM7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BT7" s="23" t="str">
+        <f t="shared" si="3"/>
         <v>J</v>
       </c>
-      <c r="BN7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BU7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>V</v>
       </c>
-      <c r="BO7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BV7" s="22" t="str">
+        <f t="shared" si="3"/>
         <v>S</v>
       </c>
-      <c r="BP7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BW7" s="22" t="str">
+        <f t="shared" ref="BW7:DJ7" si="4">(UPPER(LEFT(TEXT(BW6,"DDD"))))</f>
         <v>D</v>
       </c>
-      <c r="BQ7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BX7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>L</v>
       </c>
-      <c r="BR7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="BY7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="BS7" s="23" t="str">
-        <f t="shared" si="43"/>
+      <c r="BZ7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="BT7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="CA7" s="23" t="str">
+        <f t="shared" si="4"/>
         <v>J</v>
       </c>
-      <c r="BU7" s="22" t="str">
-        <f t="shared" si="43"/>
+      <c r="CB7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>V</v>
       </c>
-      <c r="BV7" s="22" t="str">
-        <f t="shared" ref="BV7:DI7" si="44">(UPPER(LEFT(TEXT(BV6,"DDD"))))</f>
+      <c r="CC7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
-      <c r="BW7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CD7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
-      <c r="BX7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CE7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>L</v>
       </c>
-      <c r="BY7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CF7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="BZ7" s="23" t="str">
-        <f t="shared" si="44"/>
+      <c r="CG7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="CA7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CH7" s="22" t="str">
+        <f t="shared" si="4"/>
         <v>J</v>
       </c>
-      <c r="CB7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CI7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>V</v>
       </c>
-      <c r="CC7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CJ7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
-      <c r="CD7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CK7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
-      <c r="CE7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CL7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>L</v>
       </c>
-      <c r="CF7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CM7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="CG7" s="22" t="str">
-        <f t="shared" si="44"/>
+      <c r="CN7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="CH7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CO7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>J</v>
       </c>
-      <c r="CI7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CP7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>V</v>
       </c>
-      <c r="CJ7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CQ7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
-      <c r="CK7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CR7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
-      <c r="CL7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CS7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>L</v>
       </c>
-      <c r="CM7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CT7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="CN7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CU7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="CO7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CV7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>J</v>
       </c>
-      <c r="CP7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CW7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>V</v>
       </c>
-      <c r="CQ7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CX7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
-      <c r="CR7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CY7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
-      <c r="CS7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="CZ7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>L</v>
       </c>
-      <c r="CT7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DA7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="CU7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DB7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="CV7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DC7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>J</v>
       </c>
-      <c r="CW7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DD7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>V</v>
       </c>
-      <c r="CX7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DE7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>S</v>
       </c>
-      <c r="CY7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DF7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>D</v>
       </c>
-      <c r="CZ7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DG7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>L</v>
       </c>
-      <c r="DA7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DH7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="DB7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DI7" s="42" t="str">
+        <f t="shared" si="4"/>
         <v>M</v>
       </c>
-      <c r="DC7" s="42" t="str">
-        <f t="shared" si="44"/>
+      <c r="DJ7" s="51" t="str">
+        <f t="shared" si="4"/>
         <v>J</v>
       </c>
-      <c r="DD7" s="42" t="str">
-        <f t="shared" si="44"/>
-        <v>V</v>
-      </c>
-      <c r="DE7" s="42" t="str">
-        <f t="shared" si="44"/>
-        <v>S</v>
-      </c>
-      <c r="DF7" s="42" t="str">
-        <f t="shared" si="44"/>
-        <v>D</v>
-      </c>
-      <c r="DG7" s="42" t="str">
-        <f t="shared" si="44"/>
-        <v>L</v>
-      </c>
-      <c r="DH7" s="42" t="str">
-        <f t="shared" si="44"/>
-        <v>M</v>
-      </c>
-      <c r="DI7" s="51" t="str">
-        <f t="shared" si="44"/>
-        <v>M</v>
-      </c>
     </row>
-    <row r="8" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B8" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10">
-        <f>SUM(D9:D16)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="11">
-        <f>SUM(E9:E16)/8</f>
-        <v>0.375</v>
-      </c>
-      <c r="F8" s="12">
+        <v>6</v>
+      </c>
+      <c r="C8" s="54"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="54">
+        <f>SUM(E9:E16)</f>
+        <v>27</v>
+      </c>
+      <c r="F8" s="11">
+        <f>SUM(F9:F16)/8</f>
+        <v>1</v>
+      </c>
+      <c r="G8" s="12">
         <v>46244</v>
       </c>
-      <c r="G8" s="30">
+      <c r="H8" s="30">
         <v>46272</v>
       </c>
-      <c r="H8" s="37"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="21"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="34"/>
       <c r="K8" s="21"/>
       <c r="L8" s="21"/>
       <c r="M8" s="21"/>
@@ -2323,9 +2358,9 @@
       <c r="CC8" s="21"/>
       <c r="CD8" s="21"/>
       <c r="CE8" s="21"/>
-      <c r="CF8" s="41"/>
-      <c r="CG8" s="21"/>
-      <c r="CH8" s="45"/>
+      <c r="CF8" s="21"/>
+      <c r="CG8" s="41"/>
+      <c r="CH8" s="21"/>
       <c r="CI8" s="45"/>
       <c r="CJ8" s="45"/>
       <c r="CK8" s="45"/>
@@ -2352,28 +2387,31 @@
       <c r="DF8" s="45"/>
       <c r="DG8" s="45"/>
       <c r="DH8" s="45"/>
-      <c r="DI8" s="46"/>
+      <c r="DI8" s="45"/>
+      <c r="DJ8" s="46"/>
     </row>
-    <row r="9" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B9" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="9"/>
-      <c r="E9" s="7">
+        <v>7</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="9">
+        <v>4</v>
+      </c>
+      <c r="F9" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="8">
+      <c r="G9" s="8">
         <v>46244</v>
       </c>
-      <c r="G9" s="31">
+      <c r="H9" s="31">
         <v>46251</v>
       </c>
-      <c r="H9" s="37"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="6"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="35"/>
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
       <c r="M9" s="6"/>
@@ -2447,9 +2485,9 @@
       <c r="CC9" s="6"/>
       <c r="CD9" s="6"/>
       <c r="CE9" s="6"/>
-      <c r="CF9" s="21"/>
-      <c r="CG9" s="6"/>
-      <c r="CH9" s="40"/>
+      <c r="CF9" s="6"/>
+      <c r="CG9" s="21"/>
+      <c r="CH9" s="6"/>
       <c r="CI9" s="40"/>
       <c r="CJ9" s="40"/>
       <c r="CK9" s="40"/>
@@ -2476,28 +2514,31 @@
       <c r="DF9" s="40"/>
       <c r="DG9" s="40"/>
       <c r="DH9" s="40"/>
-      <c r="DI9" s="47"/>
+      <c r="DI9" s="40"/>
+      <c r="DJ9" s="47"/>
     </row>
-    <row r="10" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B10" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F10" s="8">
+        <v>8</v>
+      </c>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="9">
+        <v>4</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1</v>
+      </c>
+      <c r="G10" s="8">
         <v>46251</v>
       </c>
-      <c r="G10" s="31">
+      <c r="H10" s="31">
         <v>46261</v>
       </c>
-      <c r="H10" s="37"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="6"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="35"/>
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -2573,7 +2614,7 @@
       <c r="CE10" s="6"/>
       <c r="CF10" s="6"/>
       <c r="CG10" s="6"/>
-      <c r="CH10" s="40"/>
+      <c r="CH10" s="6"/>
       <c r="CI10" s="40"/>
       <c r="CJ10" s="40"/>
       <c r="CK10" s="40"/>
@@ -2600,28 +2641,31 @@
       <c r="DF10" s="40"/>
       <c r="DG10" s="40"/>
       <c r="DH10" s="40"/>
-      <c r="DI10" s="47"/>
+      <c r="DI10" s="40"/>
+      <c r="DJ10" s="47"/>
     </row>
-    <row r="11" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B11" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F11" s="8">
+        <v>9</v>
+      </c>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="9">
+        <v>6</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1</v>
+      </c>
+      <c r="G11" s="8">
         <v>46258</v>
       </c>
-      <c r="G11" s="31">
+      <c r="H11" s="31">
         <v>46272</v>
       </c>
-      <c r="H11" s="37"/>
-      <c r="I11" s="35"/>
-      <c r="J11" s="6"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="35"/>
       <c r="K11" s="6"/>
       <c r="L11" s="6"/>
       <c r="M11" s="6"/>
@@ -2697,7 +2741,7 @@
       <c r="CE11" s="6"/>
       <c r="CF11" s="6"/>
       <c r="CG11" s="6"/>
-      <c r="CH11" s="40"/>
+      <c r="CH11" s="6"/>
       <c r="CI11" s="40"/>
       <c r="CJ11" s="40"/>
       <c r="CK11" s="40"/>
@@ -2724,28 +2768,31 @@
       <c r="DF11" s="40"/>
       <c r="DG11" s="40"/>
       <c r="DH11" s="40"/>
-      <c r="DI11" s="47"/>
+      <c r="DI11" s="40"/>
+      <c r="DJ11" s="47"/>
     </row>
-    <row r="12" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B12" s="35" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7">
-        <v>0</v>
-      </c>
-      <c r="F12" s="8">
+        <v>10</v>
+      </c>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="9">
+        <v>2</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="8">
         <v>46258</v>
       </c>
-      <c r="G12" s="31">
+      <c r="H12" s="31">
         <v>46265</v>
       </c>
-      <c r="H12" s="37"/>
-      <c r="I12" s="35"/>
-      <c r="J12" s="6"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="35"/>
       <c r="K12" s="6"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -2821,7 +2868,7 @@
       <c r="CE12" s="6"/>
       <c r="CF12" s="6"/>
       <c r="CG12" s="6"/>
-      <c r="CH12" s="40"/>
+      <c r="CH12" s="6"/>
       <c r="CI12" s="40"/>
       <c r="CJ12" s="40"/>
       <c r="CK12" s="40"/>
@@ -2848,28 +2895,31 @@
       <c r="DF12" s="40"/>
       <c r="DG12" s="40"/>
       <c r="DH12" s="40"/>
-      <c r="DI12" s="47"/>
+      <c r="DI12" s="40"/>
+      <c r="DJ12" s="47"/>
     </row>
-    <row r="13" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B13" s="35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7">
-        <v>0</v>
-      </c>
-      <c r="F13" s="8">
+        <v>11</v>
+      </c>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="9">
+        <v>2</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="8">
         <v>46258</v>
       </c>
-      <c r="G13" s="31">
+      <c r="H13" s="31">
         <v>46265</v>
       </c>
-      <c r="H13" s="37"/>
-      <c r="I13" s="35"/>
-      <c r="J13" s="6"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="35"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -2945,7 +2995,7 @@
       <c r="CE13" s="6"/>
       <c r="CF13" s="6"/>
       <c r="CG13" s="6"/>
-      <c r="CH13" s="40"/>
+      <c r="CH13" s="6"/>
       <c r="CI13" s="40"/>
       <c r="CJ13" s="40"/>
       <c r="CK13" s="40"/>
@@ -2972,28 +3022,31 @@
       <c r="DF13" s="40"/>
       <c r="DG13" s="40"/>
       <c r="DH13" s="40"/>
-      <c r="DI13" s="47"/>
+      <c r="DI13" s="40"/>
+      <c r="DJ13" s="47"/>
     </row>
-    <row r="14" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B14" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7">
-        <v>0</v>
-      </c>
-      <c r="F14" s="8">
+        <v>12</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="9">
+        <v>4</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+      <c r="G14" s="8">
         <v>46265</v>
       </c>
-      <c r="G14" s="31">
+      <c r="H14" s="31">
         <v>46272</v>
       </c>
-      <c r="H14" s="37"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="6"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="35"/>
       <c r="K14" s="6"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
@@ -3069,7 +3122,7 @@
       <c r="CE14" s="6"/>
       <c r="CF14" s="6"/>
       <c r="CG14" s="6"/>
-      <c r="CH14" s="40"/>
+      <c r="CH14" s="6"/>
       <c r="CI14" s="40"/>
       <c r="CJ14" s="40"/>
       <c r="CK14" s="40"/>
@@ -3096,28 +3149,31 @@
       <c r="DF14" s="40"/>
       <c r="DG14" s="40"/>
       <c r="DH14" s="40"/>
-      <c r="DI14" s="47"/>
+      <c r="DI14" s="40"/>
+      <c r="DJ14" s="47"/>
     </row>
-    <row r="15" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B15" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7">
-        <v>0</v>
-      </c>
-      <c r="F15" s="8">
+        <v>13</v>
+      </c>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="9">
+        <v>2</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1</v>
+      </c>
+      <c r="G15" s="8">
         <v>46265</v>
       </c>
-      <c r="G15" s="31">
+      <c r="H15" s="31">
         <v>46272</v>
       </c>
-      <c r="H15" s="37"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="6"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="35"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6"/>
       <c r="M15" s="6"/>
@@ -3193,7 +3249,7 @@
       <c r="CE15" s="6"/>
       <c r="CF15" s="6"/>
       <c r="CG15" s="6"/>
-      <c r="CH15" s="40"/>
+      <c r="CH15" s="6"/>
       <c r="CI15" s="40"/>
       <c r="CJ15" s="40"/>
       <c r="CK15" s="40"/>
@@ -3220,28 +3276,31 @@
       <c r="DF15" s="40"/>
       <c r="DG15" s="40"/>
       <c r="DH15" s="40"/>
-      <c r="DI15" s="47"/>
+      <c r="DI15" s="40"/>
+      <c r="DJ15" s="47"/>
     </row>
-    <row r="16" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B16" s="35" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="9"/>
-      <c r="E16" s="7">
+        <v>14</v>
+      </c>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="9">
+        <v>3</v>
+      </c>
+      <c r="F16" s="7">
         <v>1</v>
       </c>
-      <c r="F16" s="8">
+      <c r="G16" s="8">
         <v>46258</v>
       </c>
-      <c r="G16" s="31">
+      <c r="H16" s="31">
         <v>46261</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="I16" s="35"/>
-      <c r="J16" s="6"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="35"/>
       <c r="K16" s="6"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -3317,7 +3376,7 @@
       <c r="CE16" s="6"/>
       <c r="CF16" s="6"/>
       <c r="CG16" s="6"/>
-      <c r="CH16" s="40"/>
+      <c r="CH16" s="6"/>
       <c r="CI16" s="40"/>
       <c r="CJ16" s="40"/>
       <c r="CK16" s="40"/>
@@ -3344,31 +3403,32 @@
       <c r="DF16" s="40"/>
       <c r="DG16" s="40"/>
       <c r="DH16" s="40"/>
-      <c r="DI16" s="47"/>
+      <c r="DI16" s="40"/>
+      <c r="DJ16" s="47"/>
     </row>
-    <row r="17" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B17" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10">
-        <f>SUM(D18:D24)</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="11">
-        <f>SUM(E18:E24)/7</f>
-        <v>0</v>
-      </c>
-      <c r="F17" s="12">
-        <f>G8</f>
+        <v>15</v>
+      </c>
+      <c r="C17" s="54"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="54">
+        <f>SUM(E18:E24)</f>
+        <v>56</v>
+      </c>
+      <c r="F17" s="11">
+        <f>SUM(F18:F24)/7</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G17" s="12">
+        <f>H8</f>
         <v>46272</v>
       </c>
-      <c r="G17" s="30">
+      <c r="H17" s="30">
         <v>46289</v>
       </c>
-      <c r="H17" s="37"/>
-      <c r="I17" s="35"/>
-      <c r="J17" s="6"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="35"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
@@ -3444,7 +3504,7 @@
       <c r="CE17" s="6"/>
       <c r="CF17" s="6"/>
       <c r="CG17" s="6"/>
-      <c r="CH17" s="40"/>
+      <c r="CH17" s="6"/>
       <c r="CI17" s="40"/>
       <c r="CJ17" s="40"/>
       <c r="CK17" s="40"/>
@@ -3471,31 +3531,34 @@
       <c r="DF17" s="40"/>
       <c r="DG17" s="40"/>
       <c r="DH17" s="40"/>
-      <c r="DI17" s="47"/>
+      <c r="DI17" s="40"/>
+      <c r="DJ17" s="47"/>
     </row>
-    <row r="18" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B18" s="35" t="s">
-        <v>39</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="9"/>
-      <c r="E18" s="7">
-        <v>0</v>
-      </c>
-      <c r="F18" s="8">
+        <v>36</v>
+      </c>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="9">
+        <v>4</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1</v>
+      </c>
+      <c r="G18" s="8">
         <v>46272</v>
       </c>
-      <c r="G18" s="31">
+      <c r="H18" s="31">
         <v>46275</v>
       </c>
-      <c r="H18" s="37"/>
-      <c r="I18" s="35"/>
-      <c r="J18" s="6"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="35"/>
       <c r="K18" s="6"/>
       <c r="L18" s="6"/>
-      <c r="N18" s="6"/>
+      <c r="M18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
       <c r="Q18" s="6"/>
@@ -3567,7 +3630,7 @@
       <c r="CE18" s="6"/>
       <c r="CF18" s="6"/>
       <c r="CG18" s="6"/>
-      <c r="CH18" s="40"/>
+      <c r="CH18" s="6"/>
       <c r="CI18" s="40"/>
       <c r="CJ18" s="40"/>
       <c r="CK18" s="40"/>
@@ -3594,28 +3657,31 @@
       <c r="DF18" s="40"/>
       <c r="DG18" s="40"/>
       <c r="DH18" s="40"/>
-      <c r="DI18" s="47"/>
+      <c r="DI18" s="40"/>
+      <c r="DJ18" s="47"/>
     </row>
-    <row r="19" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B19" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="9"/>
-      <c r="E19" s="7">
+        <v>29</v>
+      </c>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E19" s="9">
+        <v>10</v>
+      </c>
+      <c r="F19" s="7">
         <v>0</v>
       </c>
-      <c r="F19" s="8">
+      <c r="G19" s="8">
         <v>46275</v>
       </c>
-      <c r="G19" s="31">
+      <c r="H19" s="31">
         <v>46279</v>
       </c>
-      <c r="H19" s="37"/>
-      <c r="I19" s="35"/>
-      <c r="J19" s="6"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="35"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
@@ -3691,7 +3757,7 @@
       <c r="CE19" s="6"/>
       <c r="CF19" s="6"/>
       <c r="CG19" s="6"/>
-      <c r="CH19" s="40"/>
+      <c r="CH19" s="6"/>
       <c r="CI19" s="40"/>
       <c r="CJ19" s="40"/>
       <c r="CK19" s="40"/>
@@ -3718,28 +3784,31 @@
       <c r="DF19" s="40"/>
       <c r="DG19" s="40"/>
       <c r="DH19" s="40"/>
-      <c r="DI19" s="47"/>
+      <c r="DI19" s="40"/>
+      <c r="DJ19" s="47"/>
     </row>
-    <row r="20" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B20" s="35" t="s">
-        <v>33</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D20" s="9"/>
-      <c r="E20" s="7">
+        <v>30</v>
+      </c>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="9">
+        <v>2</v>
+      </c>
+      <c r="F20" s="7">
         <v>0</v>
       </c>
-      <c r="F20" s="8">
+      <c r="G20" s="8">
         <v>46275</v>
       </c>
-      <c r="G20" s="31">
+      <c r="H20" s="31">
         <v>46279</v>
       </c>
-      <c r="H20" s="37"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="6"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="35"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -3815,7 +3884,7 @@
       <c r="CE20" s="6"/>
       <c r="CF20" s="6"/>
       <c r="CG20" s="6"/>
-      <c r="CH20" s="40"/>
+      <c r="CH20" s="6"/>
       <c r="CI20" s="40"/>
       <c r="CJ20" s="40"/>
       <c r="CK20" s="40"/>
@@ -3842,28 +3911,31 @@
       <c r="DF20" s="40"/>
       <c r="DG20" s="40"/>
       <c r="DH20" s="40"/>
-      <c r="DI20" s="47"/>
+      <c r="DI20" s="40"/>
+      <c r="DJ20" s="47"/>
     </row>
-    <row r="21" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B21" s="35" t="s">
-        <v>34</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D21" s="9"/>
-      <c r="E21" s="7">
+        <v>31</v>
+      </c>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="E21" s="9">
+        <v>10</v>
+      </c>
+      <c r="F21" s="7">
         <v>0</v>
       </c>
-      <c r="F21" s="8">
+      <c r="G21" s="8">
         <v>46279</v>
       </c>
-      <c r="G21" s="31">
+      <c r="H21" s="31">
         <v>46289</v>
       </c>
-      <c r="H21" s="37"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="6"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="35"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
@@ -3939,7 +4011,7 @@
       <c r="CE21" s="6"/>
       <c r="CF21" s="6"/>
       <c r="CG21" s="6"/>
-      <c r="CH21" s="40"/>
+      <c r="CH21" s="6"/>
       <c r="CI21" s="40"/>
       <c r="CJ21" s="40"/>
       <c r="CK21" s="40"/>
@@ -3966,28 +4038,31 @@
       <c r="DF21" s="40"/>
       <c r="DG21" s="40"/>
       <c r="DH21" s="40"/>
-      <c r="DI21" s="47"/>
+      <c r="DI21" s="40"/>
+      <c r="DJ21" s="47"/>
     </row>
-    <row r="22" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B22" s="35" t="s">
-        <v>35</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7">
+        <v>32</v>
+      </c>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="9">
+        <v>10</v>
+      </c>
+      <c r="F22" s="7">
         <v>0</v>
       </c>
-      <c r="F22" s="13">
+      <c r="G22" s="13">
         <v>46279</v>
       </c>
-      <c r="G22" s="32">
+      <c r="H22" s="32">
         <v>46289</v>
       </c>
-      <c r="H22" s="37"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="6"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="35"/>
       <c r="K22" s="6"/>
       <c r="L22" s="6"/>
       <c r="M22" s="6"/>
@@ -4063,7 +4138,7 @@
       <c r="CE22" s="6"/>
       <c r="CF22" s="6"/>
       <c r="CG22" s="6"/>
-      <c r="CH22" s="40"/>
+      <c r="CH22" s="6"/>
       <c r="CI22" s="40"/>
       <c r="CJ22" s="40"/>
       <c r="CK22" s="40"/>
@@ -4090,28 +4165,31 @@
       <c r="DF22" s="40"/>
       <c r="DG22" s="40"/>
       <c r="DH22" s="40"/>
-      <c r="DI22" s="47"/>
+      <c r="DI22" s="40"/>
+      <c r="DJ22" s="47"/>
     </row>
-    <row r="23" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B23" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7">
+        <v>33</v>
+      </c>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="9">
+        <v>10</v>
+      </c>
+      <c r="F23" s="7">
         <v>0</v>
       </c>
-      <c r="F23" s="13">
+      <c r="G23" s="13">
         <v>46286</v>
       </c>
-      <c r="G23" s="32">
+      <c r="H23" s="32">
         <v>46289</v>
       </c>
-      <c r="H23" s="37"/>
-      <c r="I23" s="35"/>
-      <c r="J23" s="6"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="35"/>
       <c r="K23" s="6"/>
       <c r="L23" s="6"/>
       <c r="M23" s="6"/>
@@ -4187,7 +4265,7 @@
       <c r="CE23" s="6"/>
       <c r="CF23" s="6"/>
       <c r="CG23" s="6"/>
-      <c r="CH23" s="40"/>
+      <c r="CH23" s="6"/>
       <c r="CI23" s="40"/>
       <c r="CJ23" s="40"/>
       <c r="CK23" s="40"/>
@@ -4214,28 +4292,31 @@
       <c r="DF23" s="40"/>
       <c r="DG23" s="40"/>
       <c r="DH23" s="40"/>
-      <c r="DI23" s="47"/>
+      <c r="DI23" s="40"/>
+      <c r="DJ23" s="47"/>
     </row>
-    <row r="24" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B24" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="7">
+        <v>35</v>
+      </c>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="9">
+        <v>10</v>
+      </c>
+      <c r="F24" s="7">
         <v>0</v>
       </c>
-      <c r="F24" s="13">
+      <c r="G24" s="13">
         <v>46286</v>
       </c>
-      <c r="G24" s="32">
+      <c r="H24" s="32">
         <v>46289</v>
       </c>
-      <c r="H24" s="37"/>
-      <c r="I24" s="35"/>
-      <c r="J24" s="6"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="35"/>
       <c r="K24" s="6"/>
       <c r="L24" s="6"/>
       <c r="M24" s="6"/>
@@ -4311,7 +4392,7 @@
       <c r="CE24" s="6"/>
       <c r="CF24" s="6"/>
       <c r="CG24" s="6"/>
-      <c r="CH24" s="40"/>
+      <c r="CH24" s="6"/>
       <c r="CI24" s="40"/>
       <c r="CJ24" s="40"/>
       <c r="CK24" s="40"/>
@@ -4338,31 +4419,32 @@
       <c r="DF24" s="40"/>
       <c r="DG24" s="40"/>
       <c r="DH24" s="40"/>
-      <c r="DI24" s="47"/>
+      <c r="DI24" s="40"/>
+      <c r="DJ24" s="47"/>
     </row>
-    <row r="25" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B25" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10">
-        <f>SUM(D26:D30)</f>
+        <v>16</v>
+      </c>
+      <c r="C25" s="54"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="54">
+        <f>SUM(E26:E30)</f>
+        <v>26</v>
+      </c>
+      <c r="F25" s="11">
+        <f>SUM(F26:F30)/5</f>
         <v>0</v>
       </c>
-      <c r="E25" s="11">
-        <f>SUM(E26:E30)/5</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="12">
-        <f>G17</f>
+      <c r="G25" s="12">
+        <f>H17</f>
         <v>46289</v>
       </c>
-      <c r="G25" s="30">
+      <c r="H25" s="30">
         <v>46303</v>
       </c>
-      <c r="H25" s="37"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="6"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="35"/>
       <c r="K25" s="6"/>
       <c r="L25" s="6"/>
       <c r="M25" s="6"/>
@@ -4438,7 +4520,7 @@
       <c r="CE25" s="6"/>
       <c r="CF25" s="6"/>
       <c r="CG25" s="6"/>
-      <c r="CH25" s="40"/>
+      <c r="CH25" s="6"/>
       <c r="CI25" s="40"/>
       <c r="CJ25" s="40"/>
       <c r="CK25" s="40"/>
@@ -4465,28 +4547,33 @@
       <c r="DF25" s="40"/>
       <c r="DG25" s="40"/>
       <c r="DH25" s="40"/>
-      <c r="DI25" s="47"/>
+      <c r="DI25" s="40"/>
+      <c r="DJ25" s="47"/>
     </row>
-    <row r="26" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B26" s="35" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="9"/>
-      <c r="E26" s="7">
+        <v>47</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="9">
+        <v>10</v>
+      </c>
+      <c r="F26" s="7">
         <v>0</v>
       </c>
-      <c r="F26" s="8">
+      <c r="G26" s="8">
         <v>46289</v>
       </c>
-      <c r="G26" s="31">
-        <v>46266</v>
-      </c>
-      <c r="H26" s="37"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="6"/>
+      <c r="H26" s="31">
+        <v>46296</v>
+      </c>
+      <c r="I26" s="37"/>
+      <c r="J26" s="35"/>
       <c r="K26" s="6"/>
       <c r="L26" s="6"/>
       <c r="M26" s="6"/>
@@ -4562,7 +4649,7 @@
       <c r="CE26" s="6"/>
       <c r="CF26" s="6"/>
       <c r="CG26" s="6"/>
-      <c r="CH26" s="40"/>
+      <c r="CH26" s="6"/>
       <c r="CI26" s="40"/>
       <c r="CJ26" s="40"/>
       <c r="CK26" s="40"/>
@@ -4589,28 +4676,31 @@
       <c r="DF26" s="40"/>
       <c r="DG26" s="40"/>
       <c r="DH26" s="40"/>
-      <c r="DI26" s="47"/>
+      <c r="DI26" s="40"/>
+      <c r="DJ26" s="47"/>
     </row>
-    <row r="27" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B27" s="35" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="9"/>
-      <c r="E27" s="7">
+        <v>27</v>
+      </c>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="9">
+        <v>4</v>
+      </c>
+      <c r="F27" s="7">
         <v>0</v>
       </c>
-      <c r="F27" s="8">
+      <c r="G27" s="8">
         <v>46289</v>
       </c>
-      <c r="G27" s="31">
-        <v>46266</v>
-      </c>
-      <c r="H27" s="37"/>
-      <c r="I27" s="35"/>
-      <c r="J27" s="6"/>
+      <c r="H27" s="31">
+        <v>46296</v>
+      </c>
+      <c r="I27" s="37"/>
+      <c r="J27" s="35"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -4686,7 +4776,7 @@
       <c r="CE27" s="6"/>
       <c r="CF27" s="6"/>
       <c r="CG27" s="6"/>
-      <c r="CH27" s="40"/>
+      <c r="CH27" s="6"/>
       <c r="CI27" s="40"/>
       <c r="CJ27" s="40"/>
       <c r="CK27" s="40"/>
@@ -4713,28 +4803,31 @@
       <c r="DF27" s="40"/>
       <c r="DG27" s="40"/>
       <c r="DH27" s="40"/>
-      <c r="DI27" s="47"/>
+      <c r="DI27" s="40"/>
+      <c r="DJ27" s="47"/>
     </row>
-    <row r="28" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B28" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D28" s="9"/>
-      <c r="E28" s="7">
+        <v>17</v>
+      </c>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E28" s="9">
+        <v>4</v>
+      </c>
+      <c r="F28" s="7">
         <v>0</v>
       </c>
-      <c r="F28" s="8">
-        <v>46266</v>
-      </c>
-      <c r="G28" s="31">
-        <v>46273</v>
-      </c>
-      <c r="H28" s="37"/>
-      <c r="I28" s="35"/>
-      <c r="J28" s="6"/>
+      <c r="G28" s="8">
+        <v>46296</v>
+      </c>
+      <c r="H28" s="31">
+        <v>46303</v>
+      </c>
+      <c r="I28" s="37"/>
+      <c r="J28" s="35"/>
       <c r="K28" s="6"/>
       <c r="L28" s="6"/>
       <c r="M28" s="6"/>
@@ -4810,7 +4903,7 @@
       <c r="CE28" s="6"/>
       <c r="CF28" s="6"/>
       <c r="CG28" s="6"/>
-      <c r="CH28" s="40"/>
+      <c r="CH28" s="6"/>
       <c r="CI28" s="40"/>
       <c r="CJ28" s="40"/>
       <c r="CK28" s="40"/>
@@ -4837,28 +4930,31 @@
       <c r="DF28" s="40"/>
       <c r="DG28" s="40"/>
       <c r="DH28" s="40"/>
-      <c r="DI28" s="47"/>
+      <c r="DI28" s="40"/>
+      <c r="DJ28" s="47"/>
     </row>
-    <row r="29" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B29" s="35" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D29" s="9"/>
-      <c r="E29" s="7">
+        <v>18</v>
+      </c>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E29" s="9">
+        <v>4</v>
+      </c>
+      <c r="F29" s="7">
         <v>0</v>
       </c>
-      <c r="F29" s="8">
-        <v>46266</v>
-      </c>
-      <c r="G29" s="31">
-        <v>46273</v>
-      </c>
-      <c r="H29" s="37"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="6"/>
+      <c r="G29" s="8">
+        <v>46296</v>
+      </c>
+      <c r="H29" s="31">
+        <v>46303</v>
+      </c>
+      <c r="I29" s="37"/>
+      <c r="J29" s="35"/>
       <c r="K29" s="6"/>
       <c r="L29" s="6"/>
       <c r="M29" s="6"/>
@@ -4934,7 +5030,7 @@
       <c r="CE29" s="6"/>
       <c r="CF29" s="6"/>
       <c r="CG29" s="6"/>
-      <c r="CH29" s="40"/>
+      <c r="CH29" s="6"/>
       <c r="CI29" s="40"/>
       <c r="CJ29" s="40"/>
       <c r="CK29" s="40"/>
@@ -4961,28 +5057,31 @@
       <c r="DF29" s="40"/>
       <c r="DG29" s="40"/>
       <c r="DH29" s="40"/>
-      <c r="DI29" s="47"/>
+      <c r="DI29" s="40"/>
+      <c r="DJ29" s="47"/>
     </row>
-    <row r="30" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B30" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D30" s="9"/>
-      <c r="E30" s="7">
+        <v>19</v>
+      </c>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E30" s="9">
+        <v>4</v>
+      </c>
+      <c r="F30" s="7">
         <v>0</v>
       </c>
-      <c r="F30" s="8">
-        <v>46266</v>
-      </c>
-      <c r="G30" s="31">
-        <v>46273</v>
-      </c>
-      <c r="H30" s="37"/>
-      <c r="I30" s="35"/>
-      <c r="J30" s="6"/>
+      <c r="G30" s="8">
+        <v>46296</v>
+      </c>
+      <c r="H30" s="31">
+        <v>46303</v>
+      </c>
+      <c r="I30" s="37"/>
+      <c r="J30" s="35"/>
       <c r="K30" s="6"/>
       <c r="L30" s="6"/>
       <c r="M30" s="6"/>
@@ -5058,7 +5157,7 @@
       <c r="CE30" s="6"/>
       <c r="CF30" s="6"/>
       <c r="CG30" s="6"/>
-      <c r="CH30" s="40"/>
+      <c r="CH30" s="6"/>
       <c r="CI30" s="40"/>
       <c r="CJ30" s="40"/>
       <c r="CK30" s="40"/>
@@ -5085,31 +5184,32 @@
       <c r="DF30" s="40"/>
       <c r="DG30" s="40"/>
       <c r="DH30" s="40"/>
-      <c r="DI30" s="47"/>
+      <c r="DI30" s="40"/>
+      <c r="DJ30" s="47"/>
     </row>
-    <row r="31" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B31" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10">
-        <f>SUM(D32:D37)</f>
+        <v>37</v>
+      </c>
+      <c r="C31" s="54"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="54">
+        <f>SUM(E32:E37)</f>
+        <v>50</v>
+      </c>
+      <c r="F31" s="11">
+        <f>SUM(F32:F37)/6</f>
         <v>0</v>
       </c>
-      <c r="E31" s="11">
-        <f>SUM(E32:E37)/6</f>
-        <v>0</v>
-      </c>
-      <c r="F31" s="12">
-        <f>G25</f>
+      <c r="G31" s="12">
+        <f>H25</f>
         <v>46303</v>
       </c>
-      <c r="G31" s="30">
+      <c r="H31" s="30">
         <v>46324</v>
       </c>
-      <c r="H31" s="37"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="6"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="35"/>
       <c r="K31" s="6"/>
       <c r="L31" s="6"/>
       <c r="M31" s="6"/>
@@ -5185,7 +5285,7 @@
       <c r="CE31" s="6"/>
       <c r="CF31" s="6"/>
       <c r="CG31" s="6"/>
-      <c r="CH31" s="40"/>
+      <c r="CH31" s="6"/>
       <c r="CI31" s="40"/>
       <c r="CJ31" s="40"/>
       <c r="CK31" s="40"/>
@@ -5212,26 +5312,33 @@
       <c r="DF31" s="40"/>
       <c r="DG31" s="40"/>
       <c r="DH31" s="40"/>
-      <c r="DI31" s="47"/>
+      <c r="DI31" s="40"/>
+      <c r="DJ31" s="47"/>
     </row>
-    <row r="32" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B32" s="35" t="s">
-        <v>41</v>
-      </c>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="7">
+        <v>38</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="9">
+        <v>4</v>
+      </c>
+      <c r="F32" s="7">
         <v>0</v>
       </c>
-      <c r="F32" s="14">
+      <c r="G32" s="14">
         <v>46303</v>
       </c>
-      <c r="G32" s="33">
+      <c r="H32" s="33">
         <v>46310</v>
       </c>
-      <c r="H32" s="37"/>
-      <c r="I32" s="35"/>
-      <c r="J32" s="6"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="35"/>
       <c r="K32" s="6"/>
       <c r="L32" s="6"/>
       <c r="M32" s="6"/>
@@ -5307,7 +5414,7 @@
       <c r="CE32" s="6"/>
       <c r="CF32" s="6"/>
       <c r="CG32" s="6"/>
-      <c r="CH32" s="40"/>
+      <c r="CH32" s="6"/>
       <c r="CI32" s="40"/>
       <c r="CJ32" s="40"/>
       <c r="CK32" s="40"/>
@@ -5334,26 +5441,33 @@
       <c r="DF32" s="40"/>
       <c r="DG32" s="40"/>
       <c r="DH32" s="40"/>
-      <c r="DI32" s="47"/>
+      <c r="DI32" s="40"/>
+      <c r="DJ32" s="47"/>
     </row>
-    <row r="33" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B33" s="35" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="7">
+        <v>20</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="9">
+        <v>4</v>
+      </c>
+      <c r="F33" s="7">
         <v>0</v>
       </c>
-      <c r="F33" s="14">
+      <c r="G33" s="14">
         <v>46303</v>
       </c>
-      <c r="G33" s="33">
+      <c r="H33" s="33">
         <v>46310</v>
       </c>
-      <c r="H33" s="37"/>
-      <c r="I33" s="35"/>
-      <c r="J33" s="6"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="35"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
@@ -5429,7 +5543,7 @@
       <c r="CE33" s="6"/>
       <c r="CF33" s="6"/>
       <c r="CG33" s="6"/>
-      <c r="CH33" s="40"/>
+      <c r="CH33" s="6"/>
       <c r="CI33" s="40"/>
       <c r="CJ33" s="40"/>
       <c r="CK33" s="40"/>
@@ -5456,26 +5570,31 @@
       <c r="DF33" s="40"/>
       <c r="DG33" s="40"/>
       <c r="DH33" s="40"/>
-      <c r="DI33" s="47"/>
+      <c r="DI33" s="40"/>
+      <c r="DJ33" s="47"/>
     </row>
-    <row r="34" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B34" s="35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="7">
+      <c r="D34" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="9">
+        <v>4</v>
+      </c>
+      <c r="F34" s="7">
         <v>0</v>
       </c>
-      <c r="F34" s="14">
+      <c r="G34" s="14">
         <v>46310</v>
       </c>
-      <c r="G34" s="33">
+      <c r="H34" s="33">
         <v>46317</v>
       </c>
-      <c r="H34" s="37"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="6"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="35"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
@@ -5551,7 +5670,7 @@
       <c r="CE34" s="6"/>
       <c r="CF34" s="6"/>
       <c r="CG34" s="6"/>
-      <c r="CH34" s="40"/>
+      <c r="CH34" s="6"/>
       <c r="CI34" s="40"/>
       <c r="CJ34" s="40"/>
       <c r="CK34" s="40"/>
@@ -5578,26 +5697,31 @@
       <c r="DF34" s="40"/>
       <c r="DG34" s="40"/>
       <c r="DH34" s="40"/>
-      <c r="DI34" s="47"/>
+      <c r="DI34" s="40"/>
+      <c r="DJ34" s="47"/>
     </row>
-    <row r="35" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B35" s="35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C35" s="9"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7">
+      <c r="D35" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E35" s="9">
+        <v>10</v>
+      </c>
+      <c r="F35" s="7">
         <v>0</v>
       </c>
-      <c r="F35" s="14">
+      <c r="G35" s="14">
         <v>46310</v>
       </c>
-      <c r="G35" s="33">
+      <c r="H35" s="33">
         <v>46317</v>
       </c>
-      <c r="H35" s="37"/>
-      <c r="I35" s="35"/>
-      <c r="J35" s="6"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="35"/>
       <c r="K35" s="6"/>
       <c r="L35" s="6"/>
       <c r="M35" s="6"/>
@@ -5673,7 +5797,7 @@
       <c r="CE35" s="6"/>
       <c r="CF35" s="6"/>
       <c r="CG35" s="6"/>
-      <c r="CH35" s="40"/>
+      <c r="CH35" s="6"/>
       <c r="CI35" s="40"/>
       <c r="CJ35" s="40"/>
       <c r="CK35" s="40"/>
@@ -5700,26 +5824,33 @@
       <c r="DF35" s="40"/>
       <c r="DG35" s="40"/>
       <c r="DH35" s="40"/>
-      <c r="DI35" s="47"/>
+      <c r="DI35" s="40"/>
+      <c r="DJ35" s="47"/>
     </row>
-    <row r="36" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B36" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="9"/>
-      <c r="D36" s="9"/>
-      <c r="E36" s="7">
+        <v>48</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E36" s="9">
+        <v>20</v>
+      </c>
+      <c r="F36" s="7">
         <v>0</v>
       </c>
-      <c r="F36" s="14">
-        <v>46317</v>
-      </c>
-      <c r="G36" s="33">
+      <c r="G36" s="14">
+        <v>46282</v>
+      </c>
+      <c r="H36" s="33">
         <v>46321</v>
       </c>
-      <c r="H36" s="37"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="6"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="35"/>
       <c r="K36" s="6"/>
       <c r="L36" s="6"/>
       <c r="M36" s="6"/>
@@ -5795,7 +5926,7 @@
       <c r="CE36" s="6"/>
       <c r="CF36" s="6"/>
       <c r="CG36" s="6"/>
-      <c r="CH36" s="40"/>
+      <c r="CH36" s="6"/>
       <c r="CI36" s="40"/>
       <c r="CJ36" s="40"/>
       <c r="CK36" s="40"/>
@@ -5822,26 +5953,31 @@
       <c r="DF36" s="40"/>
       <c r="DG36" s="40"/>
       <c r="DH36" s="40"/>
-      <c r="DI36" s="47"/>
+      <c r="DI36" s="40"/>
+      <c r="DJ36" s="47"/>
     </row>
-    <row r="37" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B37" s="35" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C37" s="9"/>
-      <c r="D37" s="9"/>
-      <c r="E37" s="7">
+      <c r="D37" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E37" s="9">
+        <v>8</v>
+      </c>
+      <c r="F37" s="7">
         <v>0</v>
       </c>
-      <c r="F37" s="14">
+      <c r="G37" s="14">
         <v>46321</v>
       </c>
-      <c r="G37" s="33">
+      <c r="H37" s="33">
         <v>46324</v>
       </c>
-      <c r="H37" s="37"/>
-      <c r="I37" s="35"/>
-      <c r="J37" s="6"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="35"/>
       <c r="K37" s="6"/>
       <c r="L37" s="6"/>
       <c r="M37" s="6"/>
@@ -5917,7 +6053,7 @@
       <c r="CE37" s="6"/>
       <c r="CF37" s="6"/>
       <c r="CG37" s="6"/>
-      <c r="CH37" s="40"/>
+      <c r="CH37" s="6"/>
       <c r="CI37" s="40"/>
       <c r="CJ37" s="40"/>
       <c r="CK37" s="40"/>
@@ -5944,31 +6080,32 @@
       <c r="DF37" s="40"/>
       <c r="DG37" s="40"/>
       <c r="DH37" s="40"/>
-      <c r="DI37" s="47"/>
+      <c r="DI37" s="40"/>
+      <c r="DJ37" s="47"/>
     </row>
-    <row r="38" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B38" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10">
-        <f>SUM(D39:D41)</f>
+        <v>45</v>
+      </c>
+      <c r="C38" s="54"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="54">
+        <f>SUM(E39:E41)</f>
+        <v>16</v>
+      </c>
+      <c r="F38" s="11">
+        <f>SUM(F39:F40)/2</f>
         <v>0</v>
       </c>
-      <c r="E38" s="11">
-        <f>SUM(E39:E40)/2</f>
-        <v>0</v>
-      </c>
-      <c r="F38" s="12">
-        <f>G31</f>
+      <c r="G38" s="12">
+        <f>H31</f>
         <v>46324</v>
       </c>
-      <c r="G38" s="30">
+      <c r="H38" s="30">
         <v>46342</v>
       </c>
-      <c r="H38" s="37"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="6"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="35"/>
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
@@ -6044,7 +6181,7 @@
       <c r="CE38" s="6"/>
       <c r="CF38" s="6"/>
       <c r="CG38" s="6"/>
-      <c r="CH38" s="40"/>
+      <c r="CH38" s="6"/>
       <c r="CI38" s="40"/>
       <c r="CJ38" s="40"/>
       <c r="CK38" s="40"/>
@@ -6071,26 +6208,31 @@
       <c r="DF38" s="40"/>
       <c r="DG38" s="40"/>
       <c r="DH38" s="40"/>
-      <c r="DI38" s="47"/>
+      <c r="DI38" s="40"/>
+      <c r="DJ38" s="47"/>
     </row>
-    <row r="39" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B39" s="35" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C39" s="9"/>
-      <c r="D39" s="9"/>
-      <c r="E39" s="7">
+      <c r="E39" s="9">
+        <v>12</v>
+      </c>
+      <c r="F39" s="7">
         <v>0</v>
       </c>
-      <c r="F39" s="14">
+      <c r="G39" s="14">
         <v>46324</v>
       </c>
-      <c r="G39" s="33">
+      <c r="H39" s="33">
         <v>46338</v>
       </c>
-      <c r="H39" s="37"/>
-      <c r="I39" s="35"/>
-      <c r="J39" s="6"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="35"/>
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
@@ -6166,7 +6308,7 @@
       <c r="CE39" s="6"/>
       <c r="CF39" s="6"/>
       <c r="CG39" s="6"/>
-      <c r="CH39" s="40"/>
+      <c r="CH39" s="6"/>
       <c r="CI39" s="40"/>
       <c r="CJ39" s="40"/>
       <c r="CK39" s="40"/>
@@ -6193,26 +6335,31 @@
       <c r="DF39" s="40"/>
       <c r="DG39" s="40"/>
       <c r="DH39" s="40"/>
-      <c r="DI39" s="47"/>
+      <c r="DI39" s="40"/>
+      <c r="DJ39" s="47"/>
     </row>
-    <row r="40" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B40" s="35" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C40" s="9"/>
-      <c r="D40" s="9"/>
-      <c r="E40" s="7">
+      <c r="D40" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="9">
+        <v>4</v>
+      </c>
+      <c r="F40" s="7">
         <v>0</v>
       </c>
-      <c r="F40" s="14">
+      <c r="G40" s="14">
         <v>46338</v>
       </c>
-      <c r="G40" s="33">
+      <c r="H40" s="33">
         <v>46342</v>
       </c>
-      <c r="H40" s="37"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="6"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="35"/>
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -6288,7 +6435,7 @@
       <c r="CE40" s="6"/>
       <c r="CF40" s="6"/>
       <c r="CG40" s="6"/>
-      <c r="CH40" s="40"/>
+      <c r="CH40" s="6"/>
       <c r="CI40" s="40"/>
       <c r="CJ40" s="40"/>
       <c r="CK40" s="40"/>
@@ -6315,18 +6462,19 @@
       <c r="DF40" s="40"/>
       <c r="DG40" s="40"/>
       <c r="DH40" s="40"/>
-      <c r="DI40" s="47"/>
+      <c r="DI40" s="40"/>
+      <c r="DJ40" s="47"/>
     </row>
-    <row r="41" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B41" s="36"/>
-      <c r="C41" s="24"/>
+      <c r="C41" s="25"/>
       <c r="D41" s="24"/>
-      <c r="E41" s="25"/>
-      <c r="F41" s="24"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="36"/>
       <c r="K41" s="24"/>
       <c r="L41" s="24"/>
       <c r="M41" s="24"/>
@@ -6402,7 +6550,7 @@
       <c r="CE41" s="24"/>
       <c r="CF41" s="24"/>
       <c r="CG41" s="24"/>
-      <c r="CH41" s="48"/>
+      <c r="CH41" s="24"/>
       <c r="CI41" s="48"/>
       <c r="CJ41" s="48"/>
       <c r="CK41" s="48"/>
@@ -6429,44 +6577,46 @@
       <c r="DF41" s="48"/>
       <c r="DG41" s="48"/>
       <c r="DH41" s="48"/>
-      <c r="DI41" s="49"/>
+      <c r="DI41" s="48"/>
+      <c r="DJ41" s="49"/>
     </row>
-    <row r="42" spans="2:113" x14ac:dyDescent="0.3">
-      <c r="C42" s="60" t="s">
-        <v>43</v>
-      </c>
-      <c r="D42" s="60">
-        <f>D8+D17+D25+D31+D38</f>
-        <v>0</v>
+    <row r="42" spans="2:114" x14ac:dyDescent="0.25">
+      <c r="D42" s="52" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="52">
+        <f>E8+E17+E25+E31+E38</f>
+        <v>175</v>
       </c>
     </row>
-    <row r="44" spans="2:113" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:114" x14ac:dyDescent="0.25">
       <c r="B44" s="35" t="s">
-        <v>37</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="C44" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="CH5:CN5"/>
-    <mergeCell ref="CO5:CU5"/>
-    <mergeCell ref="CV5:DB5"/>
-    <mergeCell ref="DC5:DI5"/>
-    <mergeCell ref="CA5:CG5"/>
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="AK5:AQ5"/>
-    <mergeCell ref="AR5:AX5"/>
-    <mergeCell ref="AY5:BE5"/>
-    <mergeCell ref="BF5:BL5"/>
-    <mergeCell ref="BM5:BS5"/>
-    <mergeCell ref="BT5:BZ5"/>
-    <mergeCell ref="AD5:AJ5"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="I5:O5"/>
-    <mergeCell ref="P5:V5"/>
-    <mergeCell ref="W5:AC5"/>
+    <mergeCell ref="BN5:BT5"/>
+    <mergeCell ref="BU5:CA5"/>
+    <mergeCell ref="AE5:AK5"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="J5:P5"/>
+    <mergeCell ref="Q5:W5"/>
+    <mergeCell ref="X5:AD5"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="AL5:AR5"/>
+    <mergeCell ref="AS5:AY5"/>
+    <mergeCell ref="AZ5:BF5"/>
+    <mergeCell ref="BG5:BM5"/>
+    <mergeCell ref="CI5:CO5"/>
+    <mergeCell ref="CP5:CV5"/>
+    <mergeCell ref="CW5:DC5"/>
+    <mergeCell ref="DD5:DJ5"/>
+    <mergeCell ref="CB5:CH5"/>
   </mergeCells>
-  <conditionalFormatting sqref="E41">
+  <conditionalFormatting sqref="F41">
     <cfRule type="dataBar" priority="14">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6480,28 +6630,28 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I18:L18 I8:DI17 I19:DI41 N18:DI18">
+  <conditionalFormatting sqref="J18:M18 J8:DJ17 J19:DJ41 O18:DJ18">
     <cfRule type="expression" dxfId="4" priority="10">
-      <formula>AND(I$6&gt;=$F8, I$6&lt;=((($G8-$F8+1)*$E8)+$F8-1))</formula>
+      <formula>AND(J$6&gt;=$G8, J$6&lt;=((($H8-$G8+1)*$F8)+$G8-1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="3" priority="11">
-      <formula>AND(I$6&gt;=$F8, I$6&lt;=$G8)</formula>
+      <formula>AND(J$6&gt;=$G8, J$6&lt;=$H8)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4">
+  <conditionalFormatting sqref="J4">
     <cfRule type="expression" dxfId="2" priority="17">
-      <formula>AND(M$6&gt;=$F18, M$6&lt;=((($G18-$F18+1)*$E18)+$F18-1))</formula>
+      <formula>AND(N$6&gt;=$G18, N$6&lt;=((($H18-$G18+1)*$F18)+$G18-1))</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="18">
-      <formula>AND(M$6&gt;=$F18, M$6&lt;=$G18)</formula>
+      <formula>AND(N$6&gt;=$G18, N$6&lt;=$H18)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8:DI41">
+  <conditionalFormatting sqref="J8:DJ41">
     <cfRule type="expression" dxfId="0" priority="9">
-      <formula>I$6=TODAY()</formula>
+      <formula>J$6=TODAY()</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E8:E12 E32:E37 E25:E30">
+  <conditionalFormatting sqref="F8:F12 F32:F37 F25:F30">
     <cfRule type="dataBar" priority="8">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6515,7 +6665,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E17:E21">
+  <conditionalFormatting sqref="F17:F21">
     <cfRule type="dataBar" priority="7">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6529,7 +6679,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E13:E15">
+  <conditionalFormatting sqref="F13:F15">
     <cfRule type="dataBar" priority="6">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6543,7 +6693,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E16">
+  <conditionalFormatting sqref="F16">
     <cfRule type="dataBar" priority="5">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6557,7 +6707,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E22:E24">
+  <conditionalFormatting sqref="F22:F24">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6571,7 +6721,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E31">
+  <conditionalFormatting sqref="F31">
     <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6585,7 +6735,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E38">
+  <conditionalFormatting sqref="F38">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6599,7 +6749,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E39:E40">
+  <conditionalFormatting sqref="F39:F40">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -6626,16 +6776,16 @@
               <controlPr defaultSize="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
-                    <xdr:col>2</xdr:col>
+                    <xdr:col>3</xdr:col>
                     <xdr:colOff>0</xdr:colOff>
-                    <xdr:row>4</xdr:row>
-                    <xdr:rowOff>15240</xdr:rowOff>
+                    <xdr:row>3</xdr:row>
+                    <xdr:rowOff>209550</xdr:rowOff>
                   </from>
                   <to>
                     <xdr:col>8</xdr:col>
-                    <xdr:colOff>297180</xdr:colOff>
+                    <xdr:colOff>0</xdr:colOff>
                     <xdr:row>4</xdr:row>
-                    <xdr:rowOff>220980</xdr:rowOff>
+                    <xdr:rowOff>276225</xdr:rowOff>
                   </to>
                 </anchor>
               </controlPr>
@@ -6663,7 +6813,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E41</xm:sqref>
+          <xm:sqref>F41</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{195AB4B8-1354-4D48-B390-689803F9EA97}">
@@ -6680,7 +6830,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E8:E12 E32:E37 E25:E30</xm:sqref>
+          <xm:sqref>F8:F12 F32:F37 F25:F30</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{476872CB-41B9-45B5-98C7-56FAECEB8CFF}">
@@ -6697,7 +6847,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E17:E21</xm:sqref>
+          <xm:sqref>F17:F21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{CDCBC34F-837A-4DB0-96DB-58080B940EB3}">
@@ -6714,7 +6864,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E13:E15</xm:sqref>
+          <xm:sqref>F13:F15</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{744AE6C3-5BD7-44DF-928F-636D2F260202}">
@@ -6731,7 +6881,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E16</xm:sqref>
+          <xm:sqref>F16</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{AA7D227D-CF25-45FD-8854-193CB649A9D8}">
@@ -6748,7 +6898,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E22:E24</xm:sqref>
+          <xm:sqref>F22:F24</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{B202A320-8915-4706-9427-48C037FB0208}">
@@ -6765,7 +6915,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E31</xm:sqref>
+          <xm:sqref>F31</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{53D00B96-155C-45D2-9A8A-0FE3A2E085FF}">
@@ -6782,7 +6932,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E38</xm:sqref>
+          <xm:sqref>F38</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DE5E10DB-F79B-4162-A1C1-C82B6C247812}">
@@ -6799,7 +6949,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>E39:E40</xm:sqref>
+          <xm:sqref>F39:F40</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
